--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.55626324443617</v>
+        <v>5.127892777220878</v>
       </c>
       <c r="D2" t="n">
-        <v>46.35138002449867</v>
+        <v>7.532099253981035</v>
       </c>
       <c r="E2" t="n">
-        <v>19.69554818027392</v>
+        <v>3.200526579294513</v>
       </c>
       <c r="F2" t="n">
-        <v>15.60506968330288</v>
+        <v>2.535823823536719</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.52309707151453</v>
+        <v>7.235003274121111</v>
       </c>
       <c r="D3" t="n">
-        <v>44.3759122960024</v>
+        <v>7.211085748100389</v>
       </c>
       <c r="E3" t="n">
-        <v>19.69554818027392</v>
+        <v>3.200526579294513</v>
       </c>
       <c r="F3" t="n">
-        <v>15.60506968330288</v>
+        <v>2.535823823536719</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>78.28283730204662</v>
+        <v>12.72096106158258</v>
       </c>
       <c r="D4" t="n">
-        <v>78.4227605560352</v>
+        <v>12.74369859035572</v>
       </c>
       <c r="E4" t="n">
-        <v>19.69554818027392</v>
+        <v>3.200526579294513</v>
       </c>
       <c r="F4" t="n">
-        <v>15.60506968330288</v>
+        <v>2.535823823536719</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
